--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2019_tarapaca.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2019_tarapaca.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:27</t>
+    <t xml:space="preserve">2026-09-09 20:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2019_tarapaca.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2019_tarapaca.xlsx
@@ -24,24 +24,24 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Iquique</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto Hospicio</t>
   </si>
   <si>
+    <t xml:space="preserve">Pozo Almonte</t>
+  </si>
+  <si>
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
     <t xml:space="preserve">Huara</t>
   </si>
   <si>
-    <t xml:space="preserve">Iquique</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pica</t>
   </si>
   <si>
-    <t xml:space="preserve">Pozo Almonte</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:27</t>
+    <t xml:space="preserve">2026-09-18 10:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -463,7 +463,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>73.92</v>
+        <v>71.16</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +471,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>70.19</v>
+        <v>73.92</v>
       </c>
     </row>
     <row r="4">
@@ -479,7 +479,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>67.47</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>71.16</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>71.86</v>
+        <v>67.47</v>
       </c>
     </row>
     <row r="7">
@@ -503,7 +503,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>71.09</v>
+        <v>71.86</v>
       </c>
     </row>
   </sheetData>
